--- a/survey_templates/038_retail_skincare_product_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/038_retail_skincare_product_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,11 +666,7 @@
           <t>Sales Channels Other</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter the name of other sales channel not listed</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -696,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -749,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>retailer_info</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Retailer Info</t>
+          <t>Social Media</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>social_media_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Social Media Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -800,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>contact_us</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,275 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>contact_us</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>social_media_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Social Media Other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter other social media not listed</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1110,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'amazon'}</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Amazon'}</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -1156,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1173,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1190,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1207,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1224,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1241,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
